--- a/globallbz1_p_ttl_15.xlsx
+++ b/globallbz1_p_ttl_15.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,34 @@
       <c r="A12" t="inlineStr">
         <is>
           <t>D:\Documents\PycharmProjects\AdHocDSR\\ttl_long\AdHoc_Net_19.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D:\Documents\PycharmProjects\AdHocDSR\\ttl_long\AdHoc_Net_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D:\Documents\PycharmProjects\AdHocDSR\\ttl_long\AdHoc_Net_3.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D:\Documents\PycharmProjects\AdHocDSR\\ttl_long\AdHoc_Net_4.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D:\Documents\PycharmProjects\AdHocDSR\\ttl_long\AdHoc_Net_5.xlsx</t>
         </is>
       </c>
     </row>
@@ -512,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1313,6 +1341,238 @@
         <v>15</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>41</v>
+      </c>
+      <c r="B14" t="n">
+        <v>121</v>
+      </c>
+      <c r="C14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5056</v>
+      </c>
+      <c r="E14" t="n">
+        <v>113</v>
+      </c>
+      <c r="F14" t="n">
+        <v>146.2222222222222</v>
+      </c>
+      <c r="G14" t="n">
+        <v>113</v>
+      </c>
+      <c r="H14" t="n">
+        <v>116</v>
+      </c>
+      <c r="I14" t="n">
+        <v>113</v>
+      </c>
+      <c r="J14" t="n">
+        <v>211</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1594.536683554159</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>256</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2203.806193124522</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>166.8327073544929</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>40</v>
+      </c>
+      <c r="B15" t="n">
+        <v>112</v>
+      </c>
+      <c r="C15" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5056</v>
+      </c>
+      <c r="E15" t="n">
+        <v>153</v>
+      </c>
+      <c r="F15" t="n">
+        <v>231.3333333333333</v>
+      </c>
+      <c r="G15" t="n">
+        <v>153</v>
+      </c>
+      <c r="H15" t="n">
+        <v>159</v>
+      </c>
+      <c r="I15" t="n">
+        <v>153</v>
+      </c>
+      <c r="J15" t="n">
+        <v>262</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1346.502507348086</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>293</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1903.333015940501</v>
+      </c>
+      <c r="O15" t="n">
+        <v>9</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>164.02430931664983</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>39</v>
+      </c>
+      <c r="B16" t="n">
+        <v>110</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5056</v>
+      </c>
+      <c r="E16" t="n">
+        <v>116</v>
+      </c>
+      <c r="F16" t="n">
+        <v>225.3333333333333</v>
+      </c>
+      <c r="G16" t="n">
+        <v>116</v>
+      </c>
+      <c r="H16" t="n">
+        <v>126.8333333333333</v>
+      </c>
+      <c r="I16" t="n">
+        <v>116</v>
+      </c>
+      <c r="J16" t="n">
+        <v>224</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1650.896083070469</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>273</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1670.2169856155</v>
+      </c>
+      <c r="O16" t="n">
+        <v>9</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>167.2461878425074</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>35</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91</v>
+      </c>
+      <c r="C17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5052</v>
+      </c>
+      <c r="E17" t="n">
+        <v>112</v>
+      </c>
+      <c r="F17" t="n">
+        <v>226.25</v>
+      </c>
+      <c r="G17" t="n">
+        <v>112</v>
+      </c>
+      <c r="H17" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>112</v>
+      </c>
+      <c r="J17" t="n">
+        <v>212</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1455.761177970195</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>286</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1724.447438912231</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>162.84386443229494</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/globallbz1_p_ttl_15.xlsx
+++ b/globallbz1_p_ttl_15.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,6 +526,34 @@
       <c r="A16" t="inlineStr">
         <is>
           <t>D:\Documents\PycharmProjects\AdHocDSR\\ttl_long\AdHoc_Net_5.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D:\Documents\PycharmProjects\AdHocDSR\\ttl_long\AdHoc_Net_6.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D:\Documents\PycharmProjects\AdHocDSR\\ttl_long\AdHoc_Net_7.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D:\Documents\PycharmProjects\AdHocDSR\\ttl_long\AdHoc_Net_8.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D:\Documents\PycharmProjects\AdHocDSR\\ttl_long\AdHoc_Net_9.xlsx</t>
         </is>
       </c>
     </row>
@@ -540,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1573,6 +1601,238 @@
         <v>15</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>50</v>
+      </c>
+      <c r="B18" t="n">
+        <v>154</v>
+      </c>
+      <c r="C18" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5056</v>
+      </c>
+      <c r="E18" t="n">
+        <v>135</v>
+      </c>
+      <c r="F18" t="n">
+        <v>214.2083333333333</v>
+      </c>
+      <c r="G18" t="n">
+        <v>135</v>
+      </c>
+      <c r="H18" t="n">
+        <v>141.1666666666667</v>
+      </c>
+      <c r="I18" t="n">
+        <v>135</v>
+      </c>
+      <c r="J18" t="n">
+        <v>200</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1664.603906001007</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>290</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1806.380303847196</v>
+      </c>
+      <c r="O18" t="n">
+        <v>9</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>165.66492819107478</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B19" t="n">
+        <v>83</v>
+      </c>
+      <c r="C19" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5052</v>
+      </c>
+      <c r="E19" t="n">
+        <v>141</v>
+      </c>
+      <c r="F19" t="n">
+        <v>144</v>
+      </c>
+      <c r="G19" t="n">
+        <v>141</v>
+      </c>
+      <c r="H19" t="n">
+        <v>144</v>
+      </c>
+      <c r="I19" t="n">
+        <v>141</v>
+      </c>
+      <c r="J19" t="n">
+        <v>147</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1563.615510895055</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8</v>
+      </c>
+      <c r="M19" t="n">
+        <v>289</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2157.714058230691</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>169.72543814250696</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B20" t="n">
+        <v>133</v>
+      </c>
+      <c r="C20" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5060</v>
+      </c>
+      <c r="E20" t="n">
+        <v>157</v>
+      </c>
+      <c r="F20" t="n">
+        <v>226.85</v>
+      </c>
+      <c r="G20" t="n">
+        <v>160</v>
+      </c>
+      <c r="H20" t="n">
+        <v>160</v>
+      </c>
+      <c r="I20" t="n">
+        <v>160</v>
+      </c>
+      <c r="J20" t="n">
+        <v>214</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1935.720304190436</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
+        <v>291</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2058.646811275272</v>
+      </c>
+      <c r="O20" t="n">
+        <v>10</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>164.73082836364054</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>40</v>
+      </c>
+      <c r="B21" t="n">
+        <v>111</v>
+      </c>
+      <c r="C21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5060</v>
+      </c>
+      <c r="E21" t="n">
+        <v>114</v>
+      </c>
+      <c r="F21" t="n">
+        <v>206.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>114</v>
+      </c>
+      <c r="H21" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="I21" t="n">
+        <v>114</v>
+      </c>
+      <c r="J21" t="n">
+        <v>234</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1575.761199799247</v>
+      </c>
+      <c r="L21" t="n">
+        <v>10</v>
+      </c>
+      <c r="M21" t="n">
+        <v>271</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2160.230200667124</v>
+      </c>
+      <c r="O21" t="n">
+        <v>10</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>162.90179875321397</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
